--- a/artfynd/A 40448-2024 artfynd.xlsx
+++ b/artfynd/A 40448-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,7 +1560,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1927714</v>
+        <v>1927715</v>
       </c>
       <c r="B9" t="n">
         <v>78569</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629721.8095541191</v>
+        <v>629722.7799882048</v>
       </c>
       <c r="R9" t="n">
-        <v>6964071.938624385</v>
+        <v>6964070.602390263</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1927715</v>
+        <v>17271765</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
+        <v>89392</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1702,37 +1702,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gåltjärnkullen NO, Ång</t>
+          <t>Gillermyrorna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629722.7799882048</v>
+        <v>629523.5163583164</v>
       </c>
       <c r="R10" t="n">
-        <v>6964070.602390263</v>
+        <v>6964120.469936636</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1756,7 +1760,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2008-10-17</t>
+          <t>2011-08-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1766,7 +1770,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2008-10-17</t>
+          <t>2011-08-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1783,39 +1787,34 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>lövrik granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Sundström, Sofia Lundell</t>
+          <t>Via Caroline Westerlund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Steget Före</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17271765</v>
+        <v>17269402</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
+        <v>78569</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,21 +1827,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1856,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629523.5163583164</v>
+        <v>629406.8407964392</v>
       </c>
       <c r="R11" t="n">
-        <v>6964120.469936636</v>
+        <v>6963832.706394097</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1937,10 +1936,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17269402</v>
+        <v>17269412</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1953,21 +1952,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2062,10 +2061,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17269412</v>
+        <v>17269409</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2078,21 +2077,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2106,10 +2105,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629406.8407964392</v>
+        <v>629523.5163583164</v>
       </c>
       <c r="R13" t="n">
-        <v>6963832.706394097</v>
+        <v>6964120.469936636</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2187,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17269409</v>
+        <v>17269432</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
+        <v>77506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2203,21 +2202,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2312,7 +2311,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17269432</v>
+        <v>17269427</v>
       </c>
       <c r="B15" t="n">
         <v>77506</v>
@@ -2356,10 +2355,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>629523.5163583164</v>
+        <v>629547.0024390569</v>
       </c>
       <c r="R15" t="n">
-        <v>6964120.469936636</v>
+        <v>6963815.777977433</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2430,131 +2429,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>17269427</v>
-      </c>
-      <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gillermyrorna, Ång</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>629547.0024390569</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6963815.777977433</v>
-      </c>
-      <c r="S16" t="n">
-        <v>100</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Härnösand</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Stigsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2011-08-15</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2011-08-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
